--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1138,6 +1138,410 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123166520</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91350</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dunby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>506016</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6568656</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123166680</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dunby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>505914</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6568574</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123166527</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dunby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>505897</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6568537</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>123166521</v>
+      </c>
+      <c r="B9" t="n">
+        <v>90952</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dunby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>506006</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6568663</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166520</v>
+        <v>123166521</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,16 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506016</v>
+        <v>506006</v>
       </c>
       <c r="R6" t="n">
-        <v>6568656</v>
+        <v>6568663</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1224,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123166680</v>
+        <v>123166527</v>
       </c>
       <c r="B7" t="n">
-        <v>97319</v>
+        <v>90972</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505914</v>
+        <v>505897</v>
       </c>
       <c r="R7" t="n">
-        <v>6568574</v>
+        <v>6568537</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166527</v>
+        <v>123166520</v>
       </c>
       <c r="B8" t="n">
-        <v>90972</v>
+        <v>91350</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,21 +1360,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505897</v>
+        <v>506016</v>
       </c>
       <c r="R8" t="n">
-        <v>6568537</v>
+        <v>6568656</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,6 +1423,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166521</v>
+        <v>123166680</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>97319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506006</v>
+        <v>505914</v>
       </c>
       <c r="R9" t="n">
-        <v>6568663</v>
+        <v>6568574</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166521</v>
+        <v>123166527</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>90972</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506006</v>
+        <v>505897</v>
       </c>
       <c r="R6" t="n">
-        <v>6568663</v>
+        <v>6568537</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123166527</v>
+        <v>123166521</v>
       </c>
       <c r="B7" t="n">
-        <v>90972</v>
+        <v>90952</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1258,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505897</v>
+        <v>506006</v>
       </c>
       <c r="R7" t="n">
-        <v>6568537</v>
+        <v>6568663</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166520</v>
+        <v>123166680</v>
       </c>
       <c r="B8" t="n">
-        <v>91350</v>
+        <v>97319</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,20 +1356,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506016</v>
+        <v>505914</v>
       </c>
       <c r="R8" t="n">
-        <v>6568656</v>
+        <v>6568574</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,7 +1428,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166680</v>
+        <v>123166520</v>
       </c>
       <c r="B9" t="n">
-        <v>97319</v>
+        <v>91350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1458,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505914</v>
+        <v>506016</v>
       </c>
       <c r="R9" t="n">
-        <v>6568574</v>
+        <v>6568656</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166527</v>
+        <v>123166521</v>
       </c>
       <c r="B6" t="n">
-        <v>90972</v>
+        <v>90952</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505897</v>
+        <v>506006</v>
       </c>
       <c r="R6" t="n">
-        <v>6568537</v>
+        <v>6568663</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123166521</v>
+        <v>123166520</v>
       </c>
       <c r="B7" t="n">
-        <v>90952</v>
+        <v>91350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,21 +1258,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1282,10 +1277,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506006</v>
+        <v>506016</v>
       </c>
       <c r="R7" t="n">
-        <v>6568663</v>
+        <v>6568656</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1326,6 +1321,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166680</v>
+        <v>123166527</v>
       </c>
       <c r="B8" t="n">
-        <v>97319</v>
+        <v>90972</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,25 +1352,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505914</v>
+        <v>505897</v>
       </c>
       <c r="R8" t="n">
-        <v>6568574</v>
+        <v>6568537</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1446,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166520</v>
+        <v>123166680</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>97319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,20 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506016</v>
+        <v>505914</v>
       </c>
       <c r="R9" t="n">
-        <v>6568656</v>
+        <v>6568574</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,7 +1526,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166521</v>
+        <v>123166680</v>
       </c>
       <c r="B6" t="n">
-        <v>90952</v>
+        <v>97322</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,25 +1152,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506006</v>
+        <v>505914</v>
       </c>
       <c r="R6" t="n">
-        <v>6568663</v>
+        <v>6568574</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1245,7 +1245,7 @@
         <v>123166520</v>
       </c>
       <c r="B7" t="n">
-        <v>91350</v>
+        <v>91353</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166527</v>
+        <v>123166521</v>
       </c>
       <c r="B8" t="n">
-        <v>90972</v>
+        <v>90955</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,21 +1356,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505897</v>
+        <v>506006</v>
       </c>
       <c r="R8" t="n">
-        <v>6568537</v>
+        <v>6568663</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166680</v>
+        <v>123166527</v>
       </c>
       <c r="B9" t="n">
-        <v>97319</v>
+        <v>90975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1454,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505914</v>
+        <v>505897</v>
       </c>
       <c r="R9" t="n">
-        <v>6568574</v>
+        <v>6568537</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166680</v>
+        <v>123166520</v>
       </c>
       <c r="B6" t="n">
-        <v>97322</v>
+        <v>91355</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1152,25 +1152,20 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1175,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505914</v>
+        <v>506016</v>
       </c>
       <c r="R6" t="n">
-        <v>6568574</v>
+        <v>6568656</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1224,6 +1219,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1242,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123166520</v>
+        <v>123166527</v>
       </c>
       <c r="B7" t="n">
-        <v>91353</v>
+        <v>90977</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1258,16 +1254,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1278,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506016</v>
+        <v>505897</v>
       </c>
       <c r="R7" t="n">
-        <v>6568656</v>
+        <v>6568537</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1322,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1340,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166521</v>
+        <v>123166680</v>
       </c>
       <c r="B8" t="n">
-        <v>90955</v>
+        <v>97324</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,25 +1352,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,10 +1380,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506006</v>
+        <v>505914</v>
       </c>
       <c r="R8" t="n">
-        <v>6568663</v>
+        <v>6568574</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166527</v>
+        <v>123166521</v>
       </c>
       <c r="B9" t="n">
-        <v>90975</v>
+        <v>90957</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505897</v>
+        <v>506006</v>
       </c>
       <c r="R9" t="n">
-        <v>6568537</v>
+        <v>6568663</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166520</v>
+        <v>123166521</v>
       </c>
       <c r="B6" t="n">
-        <v>91355</v>
+        <v>90963</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,16 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1175,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506016</v>
+        <v>506006</v>
       </c>
       <c r="R6" t="n">
-        <v>6568656</v>
+        <v>6568663</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1219,7 +1224,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1238,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123166527</v>
+        <v>123166680</v>
       </c>
       <c r="B7" t="n">
-        <v>90977</v>
+        <v>97330</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,25 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1278,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505897</v>
+        <v>505914</v>
       </c>
       <c r="R7" t="n">
-        <v>6568537</v>
+        <v>6568574</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1340,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166680</v>
+        <v>123166520</v>
       </c>
       <c r="B8" t="n">
-        <v>97324</v>
+        <v>91361</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1352,25 +1356,20 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1380,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505914</v>
+        <v>506016</v>
       </c>
       <c r="R8" t="n">
-        <v>6568574</v>
+        <v>6568656</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1424,6 +1423,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166521</v>
+        <v>123166527</v>
       </c>
       <c r="B9" t="n">
-        <v>90957</v>
+        <v>90983</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506006</v>
+        <v>505897</v>
       </c>
       <c r="R9" t="n">
-        <v>6568663</v>
+        <v>6568537</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>123166521</v>
       </c>
       <c r="B6" t="n">
-        <v>90966</v>
+        <v>90983</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1242,10 +1242,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123166520</v>
+        <v>123166680</v>
       </c>
       <c r="B7" t="n">
-        <v>91364</v>
+        <v>97350</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,20 +1254,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6040186</v>
+        <v>221945</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1277,10 +1282,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>506016</v>
+        <v>505914</v>
       </c>
       <c r="R7" t="n">
-        <v>6568656</v>
+        <v>6568574</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1321,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1343,7 +1347,7 @@
         <v>123166527</v>
       </c>
       <c r="B8" t="n">
-        <v>90986</v>
+        <v>91003</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1442,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166680</v>
+        <v>123166520</v>
       </c>
       <c r="B9" t="n">
-        <v>97333</v>
+        <v>91381</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1454,25 +1458,20 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>505914</v>
+        <v>506016</v>
       </c>
       <c r="R9" t="n">
-        <v>6568574</v>
+        <v>6568656</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1140,10 +1140,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166521</v>
+        <v>123166527</v>
       </c>
       <c r="B6" t="n">
-        <v>90983</v>
+        <v>91008</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1156,21 +1156,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>506006</v>
+        <v>505897</v>
       </c>
       <c r="R6" t="n">
-        <v>6568663</v>
+        <v>6568537</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1245,7 +1245,7 @@
         <v>123166680</v>
       </c>
       <c r="B7" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166527</v>
+        <v>123166520</v>
       </c>
       <c r="B8" t="n">
-        <v>91003</v>
+        <v>91386</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,21 +1360,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1384,10 +1379,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>505897</v>
+        <v>506016</v>
       </c>
       <c r="R8" t="n">
-        <v>6568537</v>
+        <v>6568656</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1428,6 +1423,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1446,10 +1442,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166520</v>
+        <v>123166521</v>
       </c>
       <c r="B9" t="n">
-        <v>91381</v>
+        <v>90988</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1462,16 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1481,10 +1482,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506016</v>
+        <v>506006</v>
       </c>
       <c r="R9" t="n">
-        <v>6568656</v>
+        <v>6568663</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1525,7 +1526,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -1143,7 +1143,7 @@
         <v>123166527</v>
       </c>
       <c r="B6" t="n">
-        <v>91008</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1245,7 +1245,7 @@
         <v>123166680</v>
       </c>
       <c r="B7" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1344,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166520</v>
+        <v>123166521</v>
       </c>
       <c r="B8" t="n">
-        <v>91386</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1360,16 +1360,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1379,10 +1384,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506016</v>
+        <v>506006</v>
       </c>
       <c r="R8" t="n">
-        <v>6568656</v>
+        <v>6568663</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1423,7 +1428,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1442,10 +1446,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166521</v>
+        <v>123166520</v>
       </c>
       <c r="B9" t="n">
-        <v>90988</v>
+        <v>91388</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1458,21 +1462,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1482,10 +1481,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506006</v>
+        <v>506016</v>
       </c>
       <c r="R9" t="n">
-        <v>6568663</v>
+        <v>6568656</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1526,6 +1525,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>103713886</v>
+        <v>105486652</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västra pilängen, Nrk</t>
+          <t>Kråkebo, Nrk</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>505884.815925854</v>
+        <v>506049</v>
       </c>
       <c r="R2" t="n">
-        <v>6568509.579912001</v>
+        <v>6568601</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-01-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>105138253</v>
+        <v>123166521</v>
       </c>
       <c r="B3" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,47 +784,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kråkebo, Örebro, Nrk, Nrk</t>
+          <t>Dunby, Nrk</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>506081.3391701455</v>
+        <v>506006</v>
       </c>
       <c r="R3" t="n">
-        <v>6568628.526158691</v>
+        <v>6568663</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -877,22 +838,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-12-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-12-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,27 +858,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>105485803</v>
+        <v>123166523</v>
       </c>
       <c r="B4" t="n">
-        <v>89777</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,33 +881,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kråkebo, Nrk</t>
+          <t>Dunby, Nrk</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>506036.2848676839</v>
+        <v>506026</v>
       </c>
       <c r="R4" t="n">
-        <v>6568613.113573503</v>
+        <v>6568600</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,22 +935,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,27 +955,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erik Göthlin</t>
+          <t>Frida Sjöborg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>105486652</v>
+        <v>103713886</v>
       </c>
       <c r="B5" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1043,35 +978,44 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kråkebo, Nrk</t>
+          <t>Västra pilängen, Nrk</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>506048.5978111117</v>
+        <v>505884</v>
       </c>
       <c r="R5" t="n">
-        <v>6568601.371840027</v>
+        <v>6568509</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1098,22 +1042,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-01-02</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1140,15 +1074,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123166527</v>
+        <v>103714379</v>
       </c>
       <c r="B6" t="n">
-        <v>91010</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1174,19 +1103,20 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Dunby, Nrk</t>
+          <t>Västra pilängen , Nrk</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>505897</v>
+        <v>505967</v>
       </c>
       <c r="R6" t="n">
-        <v>6568537</v>
+        <v>6568498</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,12 +1140,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1230,65 +1160,61 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123166680</v>
+        <v>104216120</v>
       </c>
       <c r="B7" t="n">
-        <v>97369</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Dunby, Nrk</t>
+          <t>Södra skogen, Nrk</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>505914</v>
+        <v>506238</v>
       </c>
       <c r="R7" t="n">
-        <v>6568574</v>
+        <v>6568272</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1312,12 +1238,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1332,27 +1258,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123166521</v>
+        <v>105138253</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1360,37 +1281,47 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Dunby, Nrk</t>
+          <t>Kråkebo, Örebro, Nrk, Nrk</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>506006</v>
+        <v>506081</v>
       </c>
       <c r="R8" t="n">
-        <v>6568663</v>
+        <v>6568629</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1414,12 +1345,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-12-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-12-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,27 +1365,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Frida Sjöborg</t>
+          <t>Erik Göthlin</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123166520</v>
+        <v>105229946</v>
       </c>
       <c r="B9" t="n">
-        <v>91388</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1462,32 +1388,47 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>5442</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Dunby, Nrk</t>
+          <t>Kråkebo, Örebro, Nrk, Nrk</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>506016</v>
+        <v>505901</v>
       </c>
       <c r="R9" t="n">
-        <v>6568656</v>
+        <v>6568722</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,12 +1452,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2022-12-18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1525,22 +1466,757 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>105230007</v>
+      </c>
+      <c r="B10" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Kråkebo, Örebro, Nrk, Nrk</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>505896</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6568727</v>
+      </c>
+      <c r="S10" t="n">
+        <v>12</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-12-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>123166527</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dunby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>505897</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6568537</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
           <t>Frida Sjöborg</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>Frida Sjöborg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126859340</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Kråkebo, Kråkebo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>506237</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6568277</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Marcus Arnesson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122703226</v>
+      </c>
+      <c r="B13" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Kråkebo, Kråkebo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>505848</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6568562</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-22</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:57</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>123166680</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dunby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>505914</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6568574</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>105485803</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Kråkebo, Nrk</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>506036</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6568613</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-01-02</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Erik Göthlin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123166520</v>
+      </c>
+      <c r="B16" t="n">
+        <v>92329</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kötticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dunby, Nrk</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>506016</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6568656</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Närke</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Frida Sjöborg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51530-2024 artfynd.xlsx
+++ b/artfynd/A 51530-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105486652</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166521</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -964,6 +979,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166523</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1071,6 +1091,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103713886</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103714379</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1267,6 +1297,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104216120</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1374,6 +1409,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105138253</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1481,6 +1521,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105229946</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1588,6 +1633,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105230007</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1685,6 +1735,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166527</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1782,6 +1837,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126859340</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1924,6 +1984,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122703226</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2021,6 +2086,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166680</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2119,6 +2189,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105485803</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2217,8 +2292,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123166520</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>